--- a/Data/EXCEL/Transfer/salemon/202512/7839-salemon-202512.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202512/7839-salemon-202512.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\202512\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202512\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5D8D182-8283-4E2E-AB62-A4CD54FECF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AADA339D-8FEF-4388-8A99-18C7863265A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="930" windowWidth="26910" windowHeight="18975" xr2:uid="{658A7459-4B3F-48AC-AD1E-0D9F56288D8F}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="17565" windowHeight="11295" xr2:uid="{5DD23E43-A1B5-4CB5-9206-00AE7377CDE0}"/>
   </bookViews>
   <sheets>
     <sheet name="7839-salemon-202512" sheetId="2" r:id="rId1"/>
@@ -845,9 +845,6 @@
     <xf numFmtId="0" fontId="22" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -857,13 +854,16 @@
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1258,20 +1258,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD713C66-C812-4F16-906C-FD86BFCE0DE2}">
-  <dimension ref="A1:Q11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A025BD2-0672-43C6-B075-07EA450240F3}">
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
-    <col min="2" max="6" width="12.125" customWidth="1"/>
-    <col min="7" max="7" width="13.875" customWidth="1"/>
-    <col min="8" max="8" width="12.75" customWidth="1"/>
-    <col min="9" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="12.75" customWidth="1"/>
-    <col min="12" max="12" width="12.125" customWidth="1"/>
-    <col min="13" max="13" width="12.75" customWidth="1"/>
-    <col min="14" max="15" width="12.125" customWidth="1"/>
-    <col min="16" max="17" width="12.75" customWidth="1"/>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
+    <col min="2" max="6" width="7.5" customWidth="1"/>
+    <col min="7" max="7" width="8.625" customWidth="1"/>
+    <col min="8" max="8" width="7.875" customWidth="1"/>
+    <col min="9" max="10" width="7.5" customWidth="1"/>
+    <col min="11" max="11" width="7.875" customWidth="1"/>
+    <col min="12" max="12" width="7.5" customWidth="1"/>
+    <col min="13" max="13" width="7.875" customWidth="1"/>
+    <col min="14" max="15" width="7.5" customWidth="1"/>
+    <col min="16" max="16" width="7.875" customWidth="1"/>
+    <col min="17" max="17" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1424,372 +1425,425 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
+        <v>45992</v>
+      </c>
+      <c r="B5" s="6">
+        <v>63</v>
+      </c>
+      <c r="C5" s="6">
+        <v>65</v>
+      </c>
+      <c r="D5" s="6">
+        <v>66</v>
+      </c>
+      <c r="E5" s="6">
+        <v>60.4</v>
+      </c>
+      <c r="F5" s="7">
+        <v>2</v>
+      </c>
+      <c r="G5" s="7">
+        <v>3.17</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1.29</v>
+      </c>
+      <c r="J5" s="7">
+        <v>5.75</v>
+      </c>
+      <c r="K5" s="8">
+        <v>1.73</v>
+      </c>
+      <c r="L5" s="7">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="N5" s="7">
+        <v>1.29</v>
+      </c>
+      <c r="O5" s="7">
+        <v>5.75</v>
+      </c>
+      <c r="P5" s="8">
+        <v>1.73</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>8.1300000000000008</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
         <v>45962</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B6" s="11">
         <v>62</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C6" s="11">
         <v>63</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D6" s="11">
         <v>66.3</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E6" s="11">
         <v>62</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F6" s="12">
         <v>1</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G6" s="12">
         <v>1.61</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H6" s="13">
         <v>0.14099999999999999</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I6" s="14">
         <v>-1.62</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J6" s="12">
         <v>8.0399999999999991</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K6" s="13">
         <v>1.59</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L6" s="12">
         <v>8.35</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M6" s="13">
         <v>0.14099999999999999</v>
       </c>
-      <c r="N5" s="9">
+      <c r="N6" s="14">
         <v>-1.62</v>
       </c>
-      <c r="O5" s="7">
+      <c r="O6" s="12">
         <v>8.0399999999999991</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P6" s="13">
         <v>1.59</v>
       </c>
-      <c r="Q5" s="7">
+      <c r="Q6" s="12">
         <v>8.35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
-        <v>45931</v>
-      </c>
-      <c r="B6" s="12">
-        <v>65.2</v>
-      </c>
-      <c r="C6" s="12">
-        <v>62</v>
-      </c>
-      <c r="D6" s="12">
-        <v>65.2</v>
-      </c>
-      <c r="E6" s="12">
-        <v>62</v>
-      </c>
-      <c r="F6" s="13">
-        <v>-3.2</v>
-      </c>
-      <c r="G6" s="13">
-        <v>-4.91</v>
-      </c>
-      <c r="H6" s="14">
-        <v>0.14299999999999999</v>
-      </c>
-      <c r="I6" s="13">
-        <v>-1.38</v>
-      </c>
-      <c r="J6" s="15">
-        <v>3.2</v>
-      </c>
-      <c r="K6" s="14">
-        <v>1.45</v>
-      </c>
-      <c r="L6" s="15">
-        <v>8.39</v>
-      </c>
-      <c r="M6" s="14">
-        <v>0.14299999999999999</v>
-      </c>
-      <c r="N6" s="13">
-        <v>-1.38</v>
-      </c>
-      <c r="O6" s="15">
-        <v>3.2</v>
-      </c>
-      <c r="P6" s="14">
-        <v>1.45</v>
-      </c>
-      <c r="Q6" s="15">
-        <v>8.39</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B7" s="6">
-        <v>67</v>
+        <v>65.2</v>
       </c>
       <c r="C7" s="6">
+        <v>62</v>
+      </c>
+      <c r="D7" s="6">
         <v>65.2</v>
-      </c>
-      <c r="D7" s="6">
-        <v>67</v>
       </c>
       <c r="E7" s="6">
         <v>62</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="15">
+        <v>-3.2</v>
+      </c>
+      <c r="G7" s="15">
+        <v>-4.91</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="I7" s="15">
+        <v>-1.38</v>
+      </c>
+      <c r="J7" s="7">
+        <v>3.2</v>
+      </c>
+      <c r="K7" s="8">
+        <v>1.45</v>
+      </c>
+      <c r="L7" s="7">
+        <v>8.39</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="N7" s="15">
+        <v>-1.38</v>
+      </c>
+      <c r="O7" s="7">
+        <v>3.2</v>
+      </c>
+      <c r="P7" s="8">
+        <v>1.45</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>8.39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
+        <v>45901</v>
+      </c>
+      <c r="B8" s="11">
+        <v>67</v>
+      </c>
+      <c r="C8" s="11">
+        <v>65.2</v>
+      </c>
+      <c r="D8" s="11">
+        <v>67</v>
+      </c>
+      <c r="E8" s="11">
+        <v>62</v>
+      </c>
+      <c r="F8" s="14">
         <v>-1.8</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G8" s="14">
         <v>-2.69</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H8" s="13">
         <v>0.14499999999999999</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I8" s="14">
         <v>-1.19</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J8" s="12">
         <v>2.77</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K8" s="13">
         <v>1.3</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L8" s="12">
         <v>8.99</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M8" s="13">
         <v>0.14499999999999999</v>
       </c>
-      <c r="N7" s="9">
+      <c r="N8" s="14">
         <v>-1.19</v>
       </c>
-      <c r="O7" s="7">
+      <c r="O8" s="12">
         <v>2.77</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P8" s="13">
         <v>1.3</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="Q8" s="12">
         <v>8.99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>45870</v>
-      </c>
-      <c r="B8" s="12">
-        <v>69</v>
-      </c>
-      <c r="C8" s="12">
-        <v>67</v>
-      </c>
-      <c r="D8" s="12">
-        <v>69</v>
-      </c>
-      <c r="E8" s="12">
-        <v>65</v>
-      </c>
-      <c r="F8" s="13">
-        <v>-2</v>
-      </c>
-      <c r="G8" s="13">
-        <v>-2.9</v>
-      </c>
-      <c r="H8" s="14">
-        <v>0.14699999999999999</v>
-      </c>
-      <c r="I8" s="13">
-        <v>-0.99</v>
-      </c>
-      <c r="J8" s="15">
-        <v>7.06</v>
-      </c>
-      <c r="K8" s="14">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="L8" s="15">
-        <v>9.82</v>
-      </c>
-      <c r="M8" s="14">
-        <v>0.14699999999999999</v>
-      </c>
-      <c r="N8" s="13">
-        <v>-0.99</v>
-      </c>
-      <c r="O8" s="15">
-        <v>7.06</v>
-      </c>
-      <c r="P8" s="14">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="Q8" s="15">
-        <v>9.82</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
+        <v>45870</v>
+      </c>
+      <c r="B9" s="6">
+        <v>69</v>
+      </c>
+      <c r="C9" s="6">
+        <v>67</v>
+      </c>
+      <c r="D9" s="6">
+        <v>69</v>
+      </c>
+      <c r="E9" s="6">
+        <v>65</v>
+      </c>
+      <c r="F9" s="15">
+        <v>-2</v>
+      </c>
+      <c r="G9" s="15">
+        <v>-2.9</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="I9" s="15">
+        <v>-0.99</v>
+      </c>
+      <c r="J9" s="7">
+        <v>7.06</v>
+      </c>
+      <c r="K9" s="8">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="L9" s="7">
+        <v>9.82</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="N9" s="15">
+        <v>-0.99</v>
+      </c>
+      <c r="O9" s="7">
+        <v>7.06</v>
+      </c>
+      <c r="P9" s="8">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>9.82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
         <v>45839</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B10" s="11">
         <v>74.599999999999994</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C10" s="11">
         <v>69</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D10" s="11">
         <v>84.7</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E10" s="11">
         <v>66</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F10" s="14">
         <v>-5.6</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G10" s="14">
         <v>-7.51</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H10" s="13">
         <v>0.14899999999999999</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I10" s="12">
         <v>6.68</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J10" s="12">
         <v>1.68</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K10" s="13">
         <v>1.01</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L10" s="12">
         <v>10.199999999999999</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M10" s="13">
         <v>0.14899999999999999</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N10" s="12">
         <v>6.68</v>
       </c>
-      <c r="O9" s="7">
+      <c r="O10" s="12">
         <v>1.68</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P10" s="13">
         <v>1.01</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="Q10" s="12">
         <v>10.199999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>45809</v>
-      </c>
-      <c r="B10" s="12">
-        <v>67</v>
-      </c>
-      <c r="C10" s="12">
-        <v>74.599999999999994</v>
-      </c>
-      <c r="D10" s="12">
-        <v>78.400000000000006</v>
-      </c>
-      <c r="E10" s="12">
-        <v>66.5</v>
-      </c>
-      <c r="F10" s="15">
-        <v>7.6</v>
-      </c>
-      <c r="G10" s="15">
-        <v>11.34</v>
-      </c>
-      <c r="H10" s="14">
-        <v>0.13900000000000001</v>
-      </c>
-      <c r="I10" s="13">
-        <v>-9.4600000000000009</v>
-      </c>
-      <c r="J10" s="15">
-        <v>9.76</v>
-      </c>
-      <c r="K10" s="14">
-        <v>0.86199999999999999</v>
-      </c>
-      <c r="L10" s="15">
-        <v>11.9</v>
-      </c>
-      <c r="M10" s="14">
-        <v>0.13900000000000001</v>
-      </c>
-      <c r="N10" s="13">
-        <v>-9.4600000000000009</v>
-      </c>
-      <c r="O10" s="15">
-        <v>9.76</v>
-      </c>
-      <c r="P10" s="14">
-        <v>0.86199999999999999</v>
-      </c>
-      <c r="Q10" s="15">
-        <v>11.9</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
+        <v>45809</v>
+      </c>
+      <c r="B11" s="6">
+        <v>67</v>
+      </c>
+      <c r="C11" s="6">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="D11" s="6">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="E11" s="6">
+        <v>66.5</v>
+      </c>
+      <c r="F11" s="7">
+        <v>7.6</v>
+      </c>
+      <c r="G11" s="7">
+        <v>11.34</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="I11" s="15">
+        <v>-9.4600000000000009</v>
+      </c>
+      <c r="J11" s="7">
+        <v>9.76</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="L11" s="7">
+        <v>11.9</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="N11" s="15">
+        <v>-9.4600000000000009</v>
+      </c>
+      <c r="O11" s="7">
+        <v>9.76</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
         <v>45778</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B12" s="11">
         <v>87</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C12" s="11">
         <v>67</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D12" s="11">
         <v>100</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E12" s="11">
         <v>65.2</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F12" s="14">
         <v>-20</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G12" s="14">
         <v>-22.99</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H12" s="13">
         <v>0.154</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J12" s="12">
         <v>7.66</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K12" s="13">
         <v>0.72199999999999998</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L12" s="12">
         <v>12.3</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M12" s="13">
         <v>0.154</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="N12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="O11" s="7">
+      <c r="O12" s="12">
         <v>7.66</v>
       </c>
-      <c r="P11" s="8">
+      <c r="P12" s="13">
         <v>0.72199999999999998</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q12" s="12">
         <v>12.3</v>
       </c>
     </row>
